--- a/inst/template/text_translations_template.xlsx
+++ b/inst/template/text_translations_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nifu-my.sharepoint.com/personal/stephan_daus_nifu_no/Documents/surveyreport/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nifu-my.sharepoint.com/personal/stephan_daus_nifu_no/Documents/surveyreport/inst/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{9737FBEC-B84E-476E-8F64-DF4B3154E557}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{21A8B0A9-9936-47A1-84E4-61A2DDA17FDB}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="8_{9737FBEC-B84E-476E-8F64-DF4B3154E557}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{294D5B25-6C6E-406B-AB08-C5579E663938}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{694E2021-33B9-4575-A588-5D588AFA8CD0}"/>
   </bookViews>
@@ -33,49 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
-  <si>
-    <t>str_agrees_sig_to</t>
-  </si>
-  <si>
-    <t>{x_val_label_focus} ({value_focus}) er signifikant {compare} enig i påstanden {y_group_label} enn {x_val_label_ref} ({value_ref}).</t>
-  </si>
-  <si>
-    <t>str_construct_fit</t>
-  </si>
-  <si>
-    <t>Samlemålet {y_group_label} har {fit} psykometriske egenskaper.</t>
-  </si>
-  <si>
-    <t>str_glue_agrees_1_above_2</t>
-  </si>
-  <si>
-    <t>{x_cat_1} er mer enig enn {tolower(x_cat_2)} i påstanden {y_label} ({p_1} kontra {p_2} prosent, en forskjell på {p_1-p_2} prosentpoeng).</t>
-  </si>
-  <si>
-    <t>{x_cat_2} er mindre enig enn {tolower(x_cat_1)} i påstanden {y_label} ({p_2} kontra {p_1} prosent, en forskjell på {p_1-p_2} prosentpoeng).</t>
-  </si>
-  <si>
-    <t>Flere {tolower(x_cat_1)} enn {tolower(x_cat_2)} er enig i påstanden {y_label} ({p_1} kontra {p_2} prosent, en forskjell på {p_1-p_2} prosentpoeng).,</t>
-  </si>
-  <si>
-    <t>Færre {tolower(x_cat_2)} enn {tolower(x_cat_1)} er enig i påstanden {y_label} ({p_2} kontra {p_1} prosent, en forskjell på {p_1-p_2} prosentpoeng).)</t>
-  </si>
-  <si>
-    <t>str_glue_likes_1_above_2</t>
-  </si>
-  <si>
-    <t>{x_cat_1} liker {y_label} mer enn {tolower(x_cat_2)} gjør ({p_1} kontra {p_2} prosent, en forskjell på {p_1-p_2} prosentpoeng).</t>
-  </si>
-  <si>
-    <t>{x_cat_2} liker {y_label} mindre enn {tolower(x_cat_1)} gjør ({p_2} kontra {p_1} prosent, en forskjell på {p_1-p_2} prosentpoeng).</t>
-  </si>
-  <si>
-    <t>Flere {tolower(x_cat_1)} enn {tolower(x_cat_2)} liker {y_label} ({p_1} kontra {p_2} prosent, en forskjell på {p_1-p_2} prosentpoeng).</t>
-  </si>
-  <si>
-    <t>Færre {tolower(x_cat_2)} enn {tolower(x_cat_1)} liker {y_label} ({p_2} kontra {p_1} prosent, en forskjell på {p_1-p_2} prosentpoeng).</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>regex</t>
   </si>
@@ -86,58 +44,49 @@
     <t>type</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>a_over_b</t>
-  </si>
-  <si>
-    <t>construct_fit</t>
-  </si>
-  <si>
-    <t>liker</t>
-  </si>
-  <si>
-    <t>{x_cat_1} synes i større grad enn {tolower(x_cat_2)} i påstanden '{tolower(y_var_label)}' ({p_1} mot {p_2} prosent).</t>
-  </si>
-  <si>
-    <t>{x_cat_2} synes i mindre grad enn {tolower(x_cat_1)} i påstanden '{tolower(y_var_label)}' ({p_2} mot {p_1} prosent).</t>
-  </si>
-  <si>
-    <t>Flere {tolower(x_cat_1)} enn {tolower(x_cat_2)} synes at '{tolower(y_var_label)}' ({p_1} mot {p_2} prosent).</t>
-  </si>
-  <si>
-    <t>Færre {tolower(x_cat_2)} enn {tolower(x_cat_1)} synes at '{tolower(y_var_label)}' ({p_2} mot {p_1} prosent).</t>
-  </si>
-  <si>
-    <t>str_glue_believes_1_above_2</t>
-  </si>
-  <si>
-    <t>synes</t>
-  </si>
-  <si>
     <t>diff</t>
   </si>
   <si>
-    <t>enig</t>
-  </si>
-  <si>
-    <t>{x_cat_1} valgte oftere enn {tolower(x_cat_2)} '{tolower(y_var_label)}' ({p_1} mot {p_2} prosent).</t>
-  </si>
-  <si>
-    <t>{x_cat_2} valgte sjeldnere enn {tolower(x_cat_1)} '{tolower(y_var_label)}' ({p_2} mot {p_1} prosent).</t>
-  </si>
-  <si>
-    <t>Flere {tolower(x_cat_1)} enn {tolower(x_cat_2)} valgte '{tolower(y_var_label)}' ({p_1} mot {p_2} prosent).</t>
-  </si>
-  <si>
-    <t>Færre {tolower(x_cat_2)} enn {tolower(x_cat_1)} valgte '{tolower(y_var_label)}' ({p_2} mot {p_1} prosent).</t>
-  </si>
-  <si>
-    <t>str_glue_checks_1_above_2</t>
-  </si>
-  <si>
-    <t>hvilke|kryss|valgte|har du</t>
+    <t>agree</t>
+  </si>
+  <si>
+    <t>like</t>
+  </si>
+  <si>
+    <t>think|believe</t>
+  </si>
+  <si>
+    <t>which|choose|prefer|tick</t>
+  </si>
+  <si>
+    <t>{x_val_label_focus} ({value_focus}) agree significantly {comp} to the claim '{y_group_label}' than {x_val_label_ref} ({value_ref}).</t>
+  </si>
+  <si>
+    <t>diff_new</t>
+  </si>
+  <si>
+    <t>{x_cat_1} are more agreeable than {tolower(x_cat_2)} to the claim {y_label} ({p_1} vs. {p_2} percent, a difference of {p_1-p_2} percentage points).</t>
+  </si>
+  <si>
+    <t>More {tolower(x_cat_1)} than {tolower(x_cat_2)} agree with the claim '{y_label}' ({p_1} vs. {p_2} percent, a difference of {p_1-p_2} percentage points).</t>
+  </si>
+  <si>
+    <t>{x_cat_1} like {y_label} more than {tolower(x_cat_2)} do ({p_1} vs. {p_2} percent, a difference of {p_1-p_2} percentage points).</t>
+  </si>
+  <si>
+    <t>More {tolower(x_cat_1)} than {tolower(x_cat_2)} like {y_label} ({p_1} vs. {p_2} percent, a difference of {p_1-p_2} percentage points).</t>
+  </si>
+  <si>
+    <t>{x_cat_1} think to a larger extent than {tolower(x_cat_2)} that '{tolower(y_var_label)}' ({p_1} vs. {p_2} percent).</t>
+  </si>
+  <si>
+    <t>More {tolower(x_cat_1)} than {tolower(x_cat_2)} think that '{tolower(y_var_label)}' ({p_1} vs. {p_2} percent).</t>
+  </si>
+  <si>
+    <t>{x_cat_1} chose more often than {tolower(x_cat_2)} '{tolower(y_var_label)}' ({p_1} vs. {p_2} percent).</t>
+  </si>
+  <si>
+    <t>More {tolower(x_cat_1)} than {tolower(x_cat_2)} chose '{tolower(y_var_label)}' ({p_1} vs. {p_2} percent).</t>
   </si>
 </sst>
 </file>
@@ -495,275 +444,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71880BA-3378-4C78-ACE2-75915AD32623}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="42.08984375" customWidth="1"/>
-    <col min="4" max="4" width="88.7265625" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="42.08984375" customWidth="1"/>
+    <col min="3" max="3" width="88.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>17</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
